--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>100</v>
+      </c>
+      <c r="I15" s="14">
+        <v>5</v>
+      </c>
+      <c r="J15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="14">
-        <v>3</v>
-      </c>
-      <c r="J15" s="14">
-        <v>1</v>
-      </c>
       <c r="K15" s="15">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>5</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>400</v>
+        <v>-60</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>112.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>71.428571428571</v>
+        <v>42.105263157894</v>
       </c>
       <c r="L16" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.285714285714</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.8</v>
+        <v>-82.119205298013</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-9.523809523809</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J17" s="14">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K17" s="15">
-        <v>-4</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.692307692307</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M17" s="15">
-        <v>166.666666666667</v>
+        <v>93.75</v>
       </c>
       <c r="N17" s="15">
-        <v>-48.936170212766</v>
+        <v>-39.215686274509</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
         <v>6</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>6.25</v>
+        <v>-15</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-29.629629629629</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>0</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M18" s="15">
-        <v>533.333333333333</v>
+        <v>340</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.647058823529</v>
+        <v>-77.083333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.040816326530</v>
+        <v>8.888888888888</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.432835820895</v>
+        <v>-10.389610389610</v>
       </c>
       <c r="L19" s="15">
-        <v>-21.621621621621</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M19" s="15">
-        <v>52.631578947368</v>
+        <v>40.816326530612</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.214285714285</v>
+        <v>-48.120300751879</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1119,19 +1119,19 @@
         <v>1</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="L20" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="M20" s="15">
         <v>-80</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.529411764705</v>
+        <v>-98.809523809523</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>26.086956521739</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="F21" s="17">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>2.970297029702</v>
+        <v>-5.504587155963</v>
       </c>
       <c r="I21" s="17">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="J21" s="17">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.790209790209</v>
+        <v>-11.931818181818</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.416666666666</v>
+        <v>-14.364640883977</v>
       </c>
       <c r="M21" s="18">
-        <v>53.571428571428</v>
+        <v>47.619047619047</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.615034168564</v>
+        <v>-70.019342359767</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
         <v>-50</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="M22" s="15">
-        <v>-66.666666666666</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
         <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="L23" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M23" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>14.285714285714</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G24" s="14">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>4.716981132075</v>
       </c>
       <c r="I24" s="14">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="J24" s="14">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.697986577181</v>
+        <v>0.588235294117</v>
       </c>
       <c r="L24" s="15">
-        <v>-20.224719101123</v>
+        <v>-25.974025974026</v>
       </c>
       <c r="M24" s="15">
-        <v>-7.792207792207</v>
+        <v>2.395209580838</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>9.523809523809</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F25" s="14">
         <v>85</v>
       </c>
       <c r="G25" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H25" s="15">
-        <v>16.438356164383</v>
+        <v>8.974358974358</v>
       </c>
       <c r="I25" s="14">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="J25" s="14">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="K25" s="15">
-        <v>5.660377358490</v>
+        <v>9.166666666666</v>
       </c>
       <c r="L25" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.497652582159</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
+        <v>11</v>
+      </c>
+      <c r="E26" s="15">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>33</v>
+      </c>
+      <c r="G26" s="14">
+        <v>30</v>
+      </c>
+      <c r="H26" s="15">
         <v>10</v>
       </c>
-      <c r="D26" s="14">
-        <v>7</v>
-      </c>
-      <c r="E26" s="15">
-        <v>42.857142857142</v>
-      </c>
-      <c r="F26" s="14">
-        <v>28</v>
-      </c>
-      <c r="G26" s="14">
-        <v>25</v>
-      </c>
-      <c r="H26" s="15">
-        <v>12</v>
-      </c>
       <c r="I26" s="14">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="J26" s="14">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.5</v>
+        <v>-1.960784313725</v>
       </c>
       <c r="L26" s="15">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.5</v>
+        <v>2.040816326530</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F27" s="14">
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-16.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L28" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1566,17 +1566,17 @@
       <c r="H31" s="15">
         <v>-100</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-60</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>42.105263157894</v>
+        <v>43.478260869565</v>
       </c>
       <c r="L16" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.896551724137</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.119205298013</v>
+        <v>-80.473372781065</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="F17" s="14">
+        <v>20</v>
+      </c>
+      <c r="G17" s="14">
+        <v>27</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-25.925925925925</v>
+      </c>
+      <c r="I17" s="14">
+        <v>39</v>
+      </c>
+      <c r="J17" s="14">
+        <v>41</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-4.878048780487</v>
+      </c>
+      <c r="L17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="14">
-        <v>17</v>
-      </c>
-      <c r="G17" s="14">
-        <v>24</v>
-      </c>
-      <c r="H17" s="15">
-        <v>-29.166666666666</v>
-      </c>
-      <c r="I17" s="14">
-        <v>31</v>
-      </c>
-      <c r="J17" s="14">
-        <v>34</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-8.823529411764</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-11.428571428571</v>
-      </c>
       <c r="M17" s="15">
-        <v>93.75</v>
+        <v>105.263157894737</v>
       </c>
       <c r="N17" s="15">
-        <v>-39.215686274509</v>
+        <v>-33.898305084745</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-15</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.333333333333</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.384615384615</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M18" s="15">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.083333333333</v>
+        <v>-77.981651376146</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H19" s="15">
-        <v>8.888888888888</v>
+        <v>19.047619047619</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="J19" s="14">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.389610389610</v>
+        <v>-8.045977011494</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.689655172413</v>
+        <v>-19.191919191919</v>
       </c>
       <c r="M19" s="15">
-        <v>40.816326530612</v>
+        <v>48.148148148148</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.120300751879</v>
+        <v>-45.205479452054</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="I20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>-88.888888888888</v>
+        <v>-70</v>
       </c>
       <c r="L20" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.809523809523</v>
+        <v>-96.907216494845</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.151515151515</v>
+        <v>29.166666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.504587155963</v>
+        <v>5.714285714285</v>
       </c>
       <c r="I21" s="17">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="J21" s="17">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.931818181818</v>
+        <v>-7.5</v>
       </c>
       <c r="L21" s="18">
-        <v>-14.364640883977</v>
+        <v>-8.866995073891</v>
       </c>
       <c r="M21" s="18">
-        <v>47.619047619047</v>
+        <v>52.892561983471</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.019342359767</v>
+        <v>-68.213058419244</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="L22" s="15">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>-61.538461538461</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
+        <v>4</v>
+      </c>
+      <c r="G23" s="14">
+        <v>4</v>
+      </c>
+      <c r="H23" s="15">
+        <v>0</v>
+      </c>
+      <c r="I23" s="14">
+        <v>9</v>
+      </c>
+      <c r="J23" s="14">
         <v>6</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
-      <c r="H23" s="15">
+      <c r="K23" s="15">
+        <v>50</v>
+      </c>
+      <c r="L23" s="15">
+        <v>80</v>
+      </c>
+      <c r="M23" s="15">
         <v>200</v>
-      </c>
-      <c r="I23" s="14">
-        <v>8</v>
-      </c>
-      <c r="J23" s="14">
-        <v>3</v>
-      </c>
-      <c r="K23" s="15">
-        <v>166.666666666667</v>
-      </c>
-      <c r="L23" s="15">
-        <v>60</v>
-      </c>
-      <c r="M23" s="15">
-        <v>700</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>-12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G24" s="14">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>4.716981132075</v>
+        <v>-0.925925925925</v>
       </c>
       <c r="I24" s="14">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="J24" s="14">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="K24" s="15">
-        <v>0.588235294117</v>
+        <v>-2.475247524752</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.974025974026</v>
+        <v>-29.893238434163</v>
       </c>
       <c r="M24" s="15">
-        <v>2.395209580838</v>
+        <v>3.141361256544</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>22</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E25" s="15">
-        <v>57.142857142857</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="F25" s="14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G25" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H25" s="15">
-        <v>8.974358974358</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="I25" s="14">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="J25" s="14">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="K25" s="15">
-        <v>9.166666666666</v>
+        <v>2.013422818791</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.497652582159</v>
+        <v>-41.312741312741</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>10</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="J26" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.960784313725</v>
+        <v>5.660377358490</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="M26" s="15">
-        <v>2.040816326530</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>3</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
+        <v>500</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>3</v>
-      </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>-57.142857142857</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -884,40 +884,40 @@
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="13" t="s">
-        <v>21</v>
+      <c r="N14" s="15">
+        <v>-100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
+        <v>20</v>
+      </c>
+      <c r="I16" s="14">
+        <v>38</v>
+      </c>
+      <c r="J16" s="14">
+        <v>28</v>
+      </c>
+      <c r="K16" s="15">
         <v>35.714285714285</v>
       </c>
-      <c r="I16" s="14">
-        <v>33</v>
-      </c>
-      <c r="J16" s="14">
-        <v>23</v>
-      </c>
-      <c r="K16" s="15">
-        <v>43.478260869565</v>
-      </c>
       <c r="L16" s="15">
-        <v>10</v>
+        <v>-5</v>
       </c>
       <c r="M16" s="15">
-        <v>-5.714285714285</v>
+        <v>-5</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.473372781065</v>
+        <v>-80.612244897959</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>14.285714285714</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H17" s="15">
-        <v>-25.925925925925</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="14">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="J17" s="14">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.878048780487</v>
+        <v>-8</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>9.523809523809</v>
       </c>
       <c r="M17" s="15">
-        <v>105.263157894737</v>
+        <v>91.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-33.898305084745</v>
+        <v>-30.303030303030</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>13.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.428571428571</v>
+        <v>-17.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.285714285714</v>
+        <v>10</v>
       </c>
       <c r="M18" s="15">
-        <v>300</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.981651376146</v>
+        <v>-72.033898305084</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F19" s="14">
+        <v>46</v>
+      </c>
+      <c r="G19" s="14">
         <v>50</v>
       </c>
-      <c r="G19" s="14">
-        <v>42</v>
-      </c>
       <c r="H19" s="15">
-        <v>19.047619047619</v>
+        <v>-8</v>
       </c>
       <c r="I19" s="14">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.045977011494</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.191919191919</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M19" s="15">
-        <v>48.148148148148</v>
+        <v>42.622950819672</v>
       </c>
       <c r="N19" s="15">
-        <v>-45.205479452054</v>
+        <v>-46.951219512195</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1119,19 +1119,19 @@
         <v>3</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="15">
-        <v>-70</v>
+        <v>-75</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-62.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.907216494845</v>
+        <v>-97.321428571428</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E21" s="18">
-        <v>29.166666666666</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G21" s="17">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="H21" s="18">
-        <v>5.714285714285</v>
+        <v>-5.833333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="J21" s="17">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.5</v>
+        <v>-11.25</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.866995073891</v>
+        <v>-9.361702127659</v>
       </c>
       <c r="M21" s="18">
-        <v>52.892561983471</v>
+        <v>50</v>
       </c>
       <c r="N21" s="18">
-        <v>-68.213058419244</v>
+        <v>-67.727272727272</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>7</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>5</v>
-      </c>
-      <c r="G22" s="14">
-        <v>5</v>
-      </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="M22" s="15">
-        <v>-38.461538461538</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J23" s="14">
         <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="M23" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>-12.5</v>
+        <v>78.260869565217</v>
       </c>
       <c r="F24" s="14">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-0.925925925925</v>
+        <v>22.115384615384</v>
       </c>
       <c r="I24" s="14">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="J24" s="14">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.475247524752</v>
+        <v>4.888888888888</v>
       </c>
       <c r="L24" s="15">
-        <v>-29.893238434163</v>
+        <v>-30.383480825958</v>
       </c>
       <c r="M24" s="15">
-        <v>3.141361256544</v>
+        <v>12.380952380952</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D25" s="14">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>-24.137931034482</v>
+        <v>55</v>
       </c>
       <c r="F25" s="14">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="G25" s="14">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H25" s="15">
-        <v>-2.439024390243</v>
+        <v>13.095238095238</v>
       </c>
       <c r="I25" s="14">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="J25" s="14">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="K25" s="15">
-        <v>2.013422818791</v>
+        <v>8.284023668639</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.312741312741</v>
+        <v>-41.346153846153</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>200</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J26" s="14">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K26" s="15">
-        <v>5.660377358490</v>
+        <v>-1.587301587301</v>
       </c>
       <c r="L26" s="15">
-        <v>-9.677419354838</v>
+        <v>-12.676056338028</v>
       </c>
       <c r="M26" s="15">
-        <v>-6.666666666666</v>
+        <v>-10.144927536231</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L27" s="15">
         <v>500</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-11.111111111111</v>
+        <v>-10</v>
       </c>
       <c r="L28" s="15">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0</v>
       </c>
       <c r="L33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>20</v>
+        <v>6.25</v>
       </c>
       <c r="I16" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K16" s="15">
-        <v>35.714285714285</v>
+        <v>40</v>
       </c>
       <c r="L16" s="15">
-        <v>-5</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M16" s="15">
-        <v>-5</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.612244897959</v>
+        <v>-81.415929203539</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>-44.444444444444</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="F17" s="14">
         <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J17" s="14">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K17" s="15">
-        <v>-8</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="L17" s="15">
-        <v>9.523809523809</v>
+        <v>-4</v>
       </c>
       <c r="M17" s="15">
-        <v>91.666666666666</v>
+        <v>84.615384615384</v>
       </c>
       <c r="N17" s="15">
-        <v>-30.303030303030</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>33.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-17.5</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="L18" s="15">
-        <v>10</v>
+        <v>2.857142857142</v>
       </c>
       <c r="M18" s="15">
-        <v>266.666666666667</v>
+        <v>260</v>
       </c>
       <c r="N18" s="15">
-        <v>-72.033898305084</v>
+        <v>-72.093023255813</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-38.888888888888</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
         <v>46</v>
       </c>
       <c r="G19" s="14">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H19" s="15">
-        <v>-8</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.142857142857</v>
+        <v>-14.166666666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.684210526315</v>
+        <v>-22.556390977443</v>
       </c>
       <c r="M19" s="15">
-        <v>42.622950819672</v>
+        <v>41.095890410958</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.951219512195</v>
+        <v>-42.777777777777</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>-75</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L20" s="15">
-        <v>-62.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-57.142857142857</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.321428571428</v>
+        <v>-95.348837209302</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>25</v>
+      </c>
+      <c r="D21" s="17">
         <v>30</v>
       </c>
-      <c r="D21" s="17">
-        <v>40</v>
-      </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G21" s="17">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.833333333333</v>
+        <v>-11.811023622047</v>
       </c>
       <c r="I21" s="17">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="J21" s="17">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.25</v>
+        <v>-10.740740740740</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.361702127659</v>
+        <v>-11.397058823529</v>
       </c>
       <c r="M21" s="18">
-        <v>50</v>
+        <v>46.951219512195</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.727272727272</v>
+        <v>-67.563930013458</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,13 +1180,13 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>7</v>
@@ -1198,19 +1198,19 @@
         <v>133.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>-10</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L22" s="15">
-        <v>-10</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M22" s="15">
-        <v>-35.714285714285</v>
+        <v>-37.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>66.666666666666</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L23" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>78.260869565217</v>
+        <v>12.121212121212</v>
       </c>
       <c r="F24" s="14">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G24" s="14">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H24" s="15">
-        <v>22.115384615384</v>
+        <v>20.183486238532</v>
       </c>
       <c r="I24" s="14">
-        <v>236</v>
+        <v>271</v>
       </c>
       <c r="J24" s="14">
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="K24" s="15">
-        <v>4.888888888888</v>
+        <v>5.038759689922</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.383480825958</v>
+        <v>-28.116710875331</v>
       </c>
       <c r="M24" s="15">
-        <v>12.380952380952</v>
+        <v>11.983471074380</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>31</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>55</v>
+        <v>34.782608695652</v>
       </c>
       <c r="F25" s="14">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G25" s="14">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H25" s="15">
-        <v>13.095238095238</v>
+        <v>23.255813953488</v>
       </c>
       <c r="I25" s="14">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="J25" s="14">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="K25" s="15">
-        <v>8.284023668639</v>
+        <v>10.9375</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.346153846153</v>
+        <v>-38.260869565217</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-10</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="J26" s="14">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.587301587301</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.676056338028</v>
+        <v>-18.823529411764</v>
       </c>
       <c r="M26" s="15">
-        <v>-10.144927536231</v>
+        <v>-8</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,19 +1397,19 @@
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="15">
         <v>500</v>
@@ -1428,11 +1428,11 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1444,16 +1444,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
+        <v>100</v>
+      </c>
+      <c r="L31" s="15">
         <v>0</v>
-      </c>
-      <c r="L31" s="15">
-        <v>-50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G16" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>6.25</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I16" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>40</v>
+        <v>40.625</v>
       </c>
       <c r="L16" s="15">
-        <v>-4.545454545454</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.695652173913</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.415929203539</v>
+        <v>-81.404958677686</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-90.909090909090</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F17" s="14">
         <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.333333333333</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="I17" s="14">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J17" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K17" s="15">
-        <v>-21.311475409836</v>
+        <v>-16.176470588235</v>
       </c>
       <c r="L17" s="15">
-        <v>-4</v>
+        <v>3.636363636363</v>
       </c>
       <c r="M17" s="15">
-        <v>84.615384615384</v>
+        <v>111.111111111111</v>
       </c>
       <c r="N17" s="15">
-        <v>-36</v>
+        <v>-26.923076923076</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F18" s="14">
         <v>17</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>21.428571428571</v>
+        <v>13.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K18" s="15">
-        <v>-12.195121951219</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>2.857142857142</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M18" s="15">
-        <v>260</v>
+        <v>185.714285714286</v>
       </c>
       <c r="N18" s="15">
-        <v>-72.093023255813</v>
+        <v>-70.588235294117</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F19" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G19" s="14">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.207547169811</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="I19" s="14">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="J19" s="14">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.166666666666</v>
+        <v>-16.546762589928</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.556390977443</v>
+        <v>-18.881118881118</v>
       </c>
       <c r="M19" s="15">
-        <v>41.095890410958</v>
+        <v>43.209876543209</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.777777777777</v>
+        <v>-42.288557213930</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="E20" s="15">
-        <v>200</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="14">
         <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>-53.846153846153</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-30</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.348837209302</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E21" s="18">
-        <v>-16.666666666666</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G21" s="17">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.811023622047</v>
+        <v>-10.852713178294</v>
       </c>
       <c r="I21" s="17">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="J21" s="17">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.740740740740</v>
+        <v>-10.819672131147</v>
       </c>
       <c r="L21" s="18">
-        <v>-11.397058823529</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="M21" s="18">
-        <v>46.951219512195</v>
+        <v>51.111111111111</v>
       </c>
       <c r="N21" s="18">
-        <v>-67.563930013458</v>
+        <v>-66.084788029925</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
+        <v>100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>9</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>350</v>
+      </c>
+      <c r="I22" s="14">
+        <v>13</v>
+      </c>
+      <c r="J22" s="14">
+        <v>12</v>
+      </c>
+      <c r="K22" s="15">
+        <v>8.333333333333</v>
+      </c>
+      <c r="L22" s="15">
         <v>0</v>
       </c>
-      <c r="F22" s="14">
-        <v>7</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
-      <c r="H22" s="15">
-        <v>133.333333333333</v>
-      </c>
-      <c r="I22" s="14">
-        <v>10</v>
-      </c>
-      <c r="J22" s="14">
-        <v>11</v>
-      </c>
-      <c r="K22" s="15">
-        <v>-9.090909090909</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-16.666666666666</v>
-      </c>
       <c r="M22" s="15">
-        <v>-37.5</v>
+        <v>-18.75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="C23" s="14">
+        <v>3</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
         <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>57.142857142857</v>
+        <v>100</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M23" s="15">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E24" s="15">
-        <v>12.121212121212</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G24" s="14">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="H24" s="15">
-        <v>20.183486238532</v>
+        <v>7.317073170731</v>
       </c>
       <c r="I24" s="14">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="J24" s="14">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="K24" s="15">
-        <v>5.038759689922</v>
+        <v>2.047781569965</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.116710875331</v>
+        <v>-31.264367816092</v>
       </c>
       <c r="M24" s="15">
-        <v>11.983471074380</v>
+        <v>13.257575757575</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E25" s="15">
-        <v>34.782608695652</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="14">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G25" s="14">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H25" s="15">
-        <v>23.255813953488</v>
+        <v>3.125</v>
       </c>
       <c r="I25" s="14">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="J25" s="14">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="K25" s="15">
-        <v>10.9375</v>
+        <v>5.555555555555</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.260869565217</v>
+        <v>-42.424242424242</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I26" s="14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="J26" s="14">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.816901408450</v>
+        <v>-1.25</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.823529411764</v>
+        <v>-15.957446808510</v>
       </c>
       <c r="M26" s="15">
-        <v>-8</v>
+        <v>-7.058823529411</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1444,16 +1444,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>66.666666666666</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,8 +1484,8 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,8 +1525,8 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1549,7 +1549,7 @@
         <v>38</v>
       </c>
       <c r="C31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>5</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
       <c r="E16" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="F16" s="14">
+        <v>17</v>
+      </c>
+      <c r="G16" s="14">
+        <v>12</v>
+      </c>
+      <c r="H16" s="15">
+        <v>41.666666666666</v>
+      </c>
+      <c r="I16" s="14">
         <v>50</v>
       </c>
-      <c r="F16" s="14">
-        <v>18</v>
-      </c>
-      <c r="G16" s="14">
-        <v>13</v>
-      </c>
-      <c r="H16" s="15">
-        <v>38.461538461538</v>
-      </c>
-      <c r="I16" s="14">
-        <v>45</v>
-      </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>40.625</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L16" s="15">
-        <v>-4.255319148936</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="M16" s="15">
-        <v>-4.255319148936</v>
+        <v>0</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.404958677686</v>
+        <v>-80.620155038759</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>14.285714285714</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H17" s="15">
-        <v>-29.411764705882</v>
+        <v>-34.210526315789</v>
       </c>
       <c r="I17" s="14">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="K17" s="15">
-        <v>-16.176470588235</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="L17" s="15">
-        <v>3.636363636363</v>
+        <v>3.076923076923</v>
       </c>
       <c r="M17" s="15">
-        <v>111.111111111111</v>
+        <v>116.129032258065</v>
       </c>
       <c r="N17" s="15">
-        <v>-26.923076923076</v>
+        <v>-21.176470588235</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-42.857142857142</v>
+        <v>150</v>
       </c>
       <c r="F18" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>13.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>-16.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="L18" s="15">
-        <v>11.111111111111</v>
+        <v>18.421052631578</v>
       </c>
       <c r="M18" s="15">
-        <v>185.714285714286</v>
+        <v>164.705882352941</v>
       </c>
       <c r="N18" s="15">
-        <v>-70.588235294117</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-31.578947368421</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G19" s="14">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.967741935483</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="I19" s="14">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="J19" s="14">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.546762589928</v>
+        <v>-16.339869281045</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.881118881118</v>
+        <v>-20</v>
       </c>
       <c r="M19" s="15">
-        <v>43.209876543209</v>
+        <v>47.126436781609</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.288557213930</v>
+        <v>-40.740740740740</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,13 +1107,13 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>50</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
         <v>7</v>
@@ -1125,13 +1125,13 @@
         <v>-46.153846153846</v>
       </c>
       <c r="L20" s="15">
-        <v>-30</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-30</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N20" s="15">
-        <v>-95</v>
+        <v>-95.569620253164</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" s="17">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E21" s="18">
-        <v>-17.142857142857</v>
+        <v>3.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G21" s="17">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.852713178294</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>272</v>
+        <v>304</v>
       </c>
       <c r="J21" s="17">
-        <v>305</v>
+        <v>335</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.819672131147</v>
+        <v>-9.253731343283</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.849315068493</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="M21" s="18">
-        <v>51.111111111111</v>
+        <v>52.763819095477</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.084788029925</v>
+        <v>-65.137614678899</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>4</v>
+      </c>
+      <c r="D22" s="14">
         <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>350</v>
+        <v>150</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K22" s="15">
-        <v>8.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M22" s="15">
-        <v>-18.75</v>
+        <v>6.25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,25 +1233,25 @@
         <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
         <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>100</v>
+        <v>114.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>27.272727272727</v>
+        <v>25</v>
       </c>
       <c r="M23" s="15">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="E24" s="15">
-        <v>-17.142857142857</v>
+        <v>-20.408163265306</v>
       </c>
       <c r="F24" s="14">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G24" s="14">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="H24" s="15">
-        <v>7.317073170731</v>
+        <v>2.857142857142</v>
       </c>
       <c r="I24" s="14">
-        <v>299</v>
+        <v>338</v>
       </c>
       <c r="J24" s="14">
-        <v>293</v>
+        <v>342</v>
       </c>
       <c r="K24" s="15">
-        <v>2.047781569965</v>
+        <v>-1.169590643274</v>
       </c>
       <c r="L24" s="15">
-        <v>-31.264367816092</v>
+        <v>-30.165289256198</v>
       </c>
       <c r="M24" s="15">
-        <v>13.257575757575</v>
+        <v>15.358361774744</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D25" s="14">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E25" s="15">
-        <v>-37.5</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="F25" s="14">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G25" s="14">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H25" s="15">
-        <v>3.125</v>
+        <v>0.952380952380</v>
       </c>
       <c r="I25" s="14">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="J25" s="14">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="K25" s="15">
-        <v>5.555555555555</v>
+        <v>1.181102362204</v>
       </c>
       <c r="L25" s="15">
-        <v>-42.424242424242</v>
+        <v>-41.986455981941</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>3.448275862068</v>
+        <v>-19.512195121951</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J26" s="14">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.25</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.957446808510</v>
+        <v>-18.867924528301</v>
       </c>
       <c r="M26" s="15">
-        <v>-7.058823529411</v>
+        <v>-11.340206185567</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>-12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>600</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,28 +1429,28 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
         <v>28.571428571428</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
       </c>
       <c r="L29" s="15">
         <v>0</v>
@@ -1500,39 +1500,39 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>2</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K15" s="15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="15">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="N15" s="15">
-        <v>250</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>41.666666666666</v>
+        <v>40</v>
       </c>
       <c r="I16" s="14">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>42.857142857142</v>
+        <v>36.842105263157</v>
       </c>
       <c r="L16" s="15">
-        <v>-3.846153846153</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="M16" s="15">
-        <v>0</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.620155038759</v>
+        <v>-81.294964028777</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E17" s="15">
-        <v>-18.181818181818</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G17" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H17" s="15">
-        <v>-34.210526315789</v>
+        <v>-26.190476190476</v>
       </c>
       <c r="I17" s="14">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J17" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.189873417721</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="L17" s="15">
-        <v>3.076923076923</v>
+        <v>14.705882352941</v>
       </c>
       <c r="M17" s="15">
-        <v>116.129032258065</v>
+        <v>143.75</v>
       </c>
       <c r="N17" s="15">
-        <v>-21.176470588235</v>
+        <v>-18.75</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>5</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
       <c r="E18" s="15">
-        <v>150</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
         <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>33.333333333333</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-10</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>18.421052631578</v>
+        <v>2.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>164.705882352941</v>
+        <v>125</v>
       </c>
       <c r="N18" s="15">
-        <v>-70</v>
+        <v>-73.214285714285</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F19" s="14">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G19" s="14">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.727272727272</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="I19" s="14">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.339869281045</v>
+        <v>-18.674698795180</v>
       </c>
       <c r="L19" s="15">
-        <v>-20</v>
+        <v>-19.161676646706</v>
       </c>
       <c r="M19" s="15">
-        <v>47.126436781609</v>
+        <v>32.352941176470</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.740740740740</v>
+        <v>-43.037974683544</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="15">
-        <v>-46.153846153846</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>-41.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-46.153846153846</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.569620253164</v>
+        <v>-95.375722543352</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E21" s="18">
-        <v>3.333333333333</v>
+        <v>-30.555555555555</v>
       </c>
       <c r="F21" s="17">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G21" s="17">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.333333333333</v>
+        <v>-16.030534351145</v>
       </c>
       <c r="I21" s="17">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="J21" s="17">
-        <v>335</v>
+        <v>371</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.253731343283</v>
+        <v>-11.859838274932</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.317073170731</v>
+        <v>-6.303724928366</v>
       </c>
       <c r="M21" s="18">
-        <v>52.763819095477</v>
+        <v>44.690265486725</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.137614678899</v>
+        <v>-65.866388308977</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>4</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>150</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>17</v>
       </c>
       <c r="J22" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K22" s="15">
-        <v>21.428571428571</v>
+        <v>6.25</v>
       </c>
       <c r="L22" s="15">
         <v>21.428571428571</v>
       </c>
       <c r="M22" s="15">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,32 +1220,32 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="I23" s="14">
         <v>15</v>
       </c>
       <c r="J23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23" s="15">
-        <v>114.285714285714</v>
+        <v>87.5</v>
       </c>
       <c r="L23" s="15">
         <v>25</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>-20.408163265306</v>
+        <v>-2.631578947368</v>
       </c>
       <c r="F24" s="14">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G24" s="14">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="H24" s="15">
-        <v>2.857142857142</v>
+        <v>-10.967741935483</v>
       </c>
       <c r="I24" s="14">
-        <v>338</v>
+        <v>372</v>
       </c>
       <c r="J24" s="14">
-        <v>342</v>
+        <v>380</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.169590643274</v>
+        <v>-2.105263157894</v>
       </c>
       <c r="L24" s="15">
-        <v>-30.165289256198</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M24" s="15">
-        <v>15.358361774744</v>
+        <v>14.461538461538</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D25" s="14">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E25" s="15">
-        <v>-23.684210526315</v>
+        <v>28</v>
       </c>
       <c r="F25" s="14">
         <v>106</v>
       </c>
       <c r="G25" s="14">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="H25" s="15">
-        <v>0.952380952380</v>
+        <v>-3.636363636363</v>
       </c>
       <c r="I25" s="14">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="J25" s="14">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="K25" s="15">
-        <v>1.181102362204</v>
+        <v>3.225806451612</v>
       </c>
       <c r="L25" s="15">
-        <v>-41.986455981941</v>
+        <v>-39.622641509434</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
         <v>8</v>
       </c>
-      <c r="D26" s="14">
-        <v>14</v>
-      </c>
       <c r="E26" s="15">
-        <v>-42.857142857142</v>
+        <v>37.5</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.512195121951</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="I26" s="14">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.510638297872</v>
+        <v>-4.901960784313</v>
       </c>
       <c r="L26" s="15">
-        <v>-18.867924528301</v>
+        <v>-13.392857142857</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.340206185567</v>
+        <v>-5.825242718446</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>200</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-12.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L27" s="15">
-        <v>133.333333333333</v>
+        <v>233.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I28" s="14">
         <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-43.75</v>
       </c>
       <c r="L28" s="15">
-        <v>28.571428571428</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="L31" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>40</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="K16" s="15">
-        <v>36.842105263157</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L16" s="15">
-        <v>-5.454545454545</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.771929824561</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.294964028777</v>
+        <v>-81.666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-15.384615384615</v>
+        <v>60</v>
       </c>
       <c r="F17" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G17" s="14">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H17" s="15">
-        <v>-26.190476190476</v>
+        <v>2.777777777777</v>
       </c>
       <c r="I17" s="14">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J17" s="14">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.217391304347</v>
+        <v>-10.309278350515</v>
       </c>
       <c r="L17" s="15">
-        <v>14.705882352941</v>
+        <v>17.567567567567</v>
       </c>
       <c r="M17" s="15">
-        <v>143.75</v>
+        <v>171.875</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.75</v>
+        <v>-14.705882352941</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-26.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K18" s="15">
-        <v>-18.181818181818</v>
+        <v>-19.298245614035</v>
       </c>
       <c r="L18" s="15">
-        <v>2.272727272727</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>125</v>
+        <v>119.047619047619</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.214285714285</v>
+        <v>-74.585635359116</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-30.769230769230</v>
+        <v>6.666666666666</v>
       </c>
       <c r="F19" s="14">
         <v>47</v>
@@ -1075,63 +1075,63 @@
         <v>-22.950819672131</v>
       </c>
       <c r="I19" s="14">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="J19" s="14">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.674698795180</v>
+        <v>-17.127071823204</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.161676646706</v>
+        <v>-17.582417582417</v>
       </c>
       <c r="M19" s="15">
-        <v>32.352941176470</v>
+        <v>32.743362831858</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.037974683544</v>
+        <v>-42.307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
         <v>5</v>
       </c>
-      <c r="G20" s="14">
-        <v>2</v>
-      </c>
       <c r="H20" s="15">
-        <v>150</v>
+        <v>-60</v>
       </c>
       <c r="I20" s="14">
         <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L20" s="15">
         <v>-42.857142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.375722543352</v>
+        <v>-95.675675675675</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>-30.555555555555</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="F21" s="17">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G21" s="17">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.030534351145</v>
+        <v>-17.164179104477</v>
       </c>
       <c r="I21" s="17">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="J21" s="17">
-        <v>371</v>
+        <v>404</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.859838274932</v>
+        <v>-12.128712871287</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.303724928366</v>
+        <v>-7.792207792207</v>
       </c>
       <c r="M21" s="18">
-        <v>44.690265486725</v>
+        <v>46.090534979423</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.866388308977</v>
+        <v>-65.667311411992</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>5</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>150</v>
       </c>
       <c r="F22" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>33.333333333333</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I22" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J22" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
-        <v>6.25</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L22" s="15">
-        <v>21.428571428571</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14">
         <v>8</v>
       </c>
       <c r="K23" s="15">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="L23" s="15">
-        <v>25</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M23" s="15">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E24" s="15">
-        <v>-2.631578947368</v>
+        <v>-6.25</v>
       </c>
       <c r="F24" s="14">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G24" s="14">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.967741935483</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="J24" s="14">
-        <v>380</v>
+        <v>412</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.105263157894</v>
+        <v>-2.427184466019</v>
       </c>
       <c r="L24" s="15">
-        <v>-29.411764705882</v>
+        <v>-28.596802841918</v>
       </c>
       <c r="M24" s="15">
-        <v>14.461538461538</v>
+        <v>18.235294117647</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E25" s="15">
-        <v>28</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="F25" s="14">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="G25" s="14">
         <v>110</v>
       </c>
       <c r="H25" s="15">
-        <v>-3.636363636363</v>
+        <v>-15.454545454545</v>
       </c>
       <c r="I25" s="14">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="J25" s="14">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="K25" s="15">
-        <v>3.225806451612</v>
+        <v>1.324503311258</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.622641509434</v>
+        <v>-40.350877192982</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>37.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.256410256410</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="I26" s="14">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="J26" s="14">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.901960784313</v>
+        <v>-12.280701754386</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.392857142857</v>
+        <v>-17.355371900826</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.825242718446</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>200</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>233.333333333333</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,28 +1429,28 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
-      <c r="F28" s="14">
-        <v>1</v>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-83.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
         <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K28" s="15">
-        <v>-43.75</v>
+        <v>-55</v>
       </c>
       <c r="L28" s="15">
         <v>-10</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>4</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
+        <v>50</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>400</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="15">
         <v>25</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-57.142857142857</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-13.333333333333</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J16" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K16" s="15">
-        <v>22.222222222222</v>
+        <v>26.086956521739</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="M16" s="15">
-        <v>-8.333333333333</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.666666666666</v>
+        <v>-82.098765432098</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G17" s="14">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="15">
-        <v>2.777777777777</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J17" s="14">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.309278350515</v>
+        <v>-10.679611650485</v>
       </c>
       <c r="L17" s="15">
-        <v>17.567567567567</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>171.875</v>
+        <v>170.588235294118</v>
       </c>
       <c r="N17" s="15">
-        <v>-14.705882352941</v>
+        <v>-16.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-37.5</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J18" s="14">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K18" s="15">
-        <v>-19.298245614035</v>
+        <v>-15</v>
       </c>
       <c r="L18" s="15">
-        <v>-4.166666666666</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="M18" s="15">
-        <v>119.047619047619</v>
+        <v>121.739130434783</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.585635359116</v>
+        <v>-74.626865671641</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>6.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.950819672131</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I19" s="14">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="J19" s="14">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K19" s="15">
-        <v>-17.127071823204</v>
+        <v>-12.765957446808</v>
       </c>
       <c r="L19" s="15">
-        <v>-17.582417582417</v>
+        <v>-15.463917525773</v>
       </c>
       <c r="M19" s="15">
-        <v>32.743362831858</v>
+        <v>35.537190082644</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.307692307692</v>
+        <v>-39.926739926739</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K20" s="15">
-        <v>-55.555555555555</v>
+        <v>-55</v>
       </c>
       <c r="L20" s="15">
-        <v>-42.857142857142</v>
+        <v>-43.75</v>
       </c>
       <c r="M20" s="15">
-        <v>-50</v>
+        <v>-43.75</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.675675675675</v>
+        <v>-95.431472081218</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.151515151515</v>
+        <v>36.842105263157</v>
       </c>
       <c r="F21" s="17">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G21" s="17">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.164179104477</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="I21" s="17">
-        <v>355</v>
+        <v>383</v>
       </c>
       <c r="J21" s="17">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.128712871287</v>
+        <v>-9.456264775413</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.792207792207</v>
+        <v>-9.456264775413</v>
       </c>
       <c r="M21" s="18">
-        <v>46.090534979423</v>
+        <v>50.196078431372</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.667311411992</v>
+        <v>-65.526552655265</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,13 +1180,13 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F22" s="14">
         <v>11</v>
@@ -1198,19 +1198,19 @@
         <v>57.142857142857</v>
       </c>
       <c r="I22" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J22" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K22" s="15">
-        <v>22.222222222222</v>
+        <v>26.315789473684</v>
       </c>
       <c r="L22" s="15">
-        <v>57.142857142857</v>
+        <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
       </c>
       <c r="H23" s="15">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" s="14">
         <v>8</v>
       </c>
       <c r="K23" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="L23" s="15">
-        <v>23.076923076923</v>
+        <v>20</v>
       </c>
       <c r="M23" s="15">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.25</v>
+        <v>8.108108108108</v>
       </c>
       <c r="F24" s="14">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="G24" s="14">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H24" s="15">
-        <v>-14.285714285714</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I24" s="14">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="J24" s="14">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.427184466019</v>
+        <v>-1.336302895322</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.596802841918</v>
+        <v>-25.795644891122</v>
       </c>
       <c r="M24" s="15">
-        <v>18.235294117647</v>
+        <v>19.407008086253</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-21.739130434782</v>
+        <v>13.636363636363</v>
       </c>
       <c r="F25" s="14">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="G25" s="14">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.454545454545</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="I25" s="14">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="J25" s="14">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="K25" s="15">
-        <v>1.324503311258</v>
+        <v>2.469135802469</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.350877192982</v>
+        <v>-38.970588235294</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-66.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.255813953488</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J26" s="14">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.280701754386</v>
+        <v>-15.702479338843</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.355371900826</v>
+        <v>-19.685039370078</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.660377358490</v>
+        <v>-8.928571428571</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+        <v>-50</v>
+      </c>
+      <c r="F28" s="14">
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" s="15">
-        <v>-55</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-90</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>3</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="15">
-        <v>80</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="15">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="N15" s="15">
-        <v>350</v>
+        <v>233.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>3</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
         <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-7.142857142857</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="I16" s="14">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J16" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>26.086956521739</v>
+        <v>20.408163265306</v>
       </c>
       <c r="L16" s="15">
-        <v>-14.705882352941</v>
+        <v>-23.376623376623</v>
       </c>
       <c r="M16" s="15">
-        <v>-3.333333333333</v>
+        <v>-9.230769230769</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.098765432098</v>
+        <v>-82.997118155619</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F17" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.571428571428</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J17" s="14">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.679611650485</v>
+        <v>-9.259259259259</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>2.083333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>170.588235294118</v>
+        <v>172.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>-16.363636363636</v>
+        <v>-14.782608695652</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-8.333333333333</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="I18" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="K18" s="15">
-        <v>-15</v>
+        <v>-24.637681159420</v>
       </c>
       <c r="L18" s="15">
-        <v>-1.923076923076</v>
+        <v>-5.454545454545</v>
       </c>
       <c r="M18" s="15">
-        <v>121.739130434783</v>
+        <v>100</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.626865671641</v>
+        <v>-76.785714285714</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="14">
         <v>14</v>
       </c>
-      <c r="D19" s="14">
-        <v>7</v>
-      </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G19" s="14">
         <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.040816326530</v>
+        <v>6.122448979591</v>
       </c>
       <c r="I19" s="14">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J19" s="14">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.765957446808</v>
+        <v>-11.386138613861</v>
       </c>
       <c r="L19" s="15">
-        <v>-15.463917525773</v>
+        <v>-12.682926829268</v>
       </c>
       <c r="M19" s="15">
-        <v>35.537190082644</v>
+        <v>42.063492063492</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.926739926739</v>
+        <v>-39.322033898305</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-71.428571428571</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>-55</v>
+        <v>-52</v>
       </c>
       <c r="L20" s="15">
-        <v>-43.75</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="M20" s="15">
-        <v>-43.75</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.431472081218</v>
+        <v>-94.258373205741</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E21" s="18">
-        <v>36.842105263157</v>
+        <v>-24.324324324324</v>
       </c>
       <c r="F21" s="17">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G21" s="17">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.474576271186</v>
+        <v>-14.4</v>
       </c>
       <c r="I21" s="17">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="J21" s="17">
-        <v>423</v>
+        <v>460</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.456264775413</v>
+        <v>-10.869565217391</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.456264775413</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M21" s="18">
-        <v>50.196078431372</v>
+        <v>51.851851851851</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.526552655265</v>
+        <v>-65.747702589807</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>200</v>
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>57.142857142857</v>
+        <v>80</v>
       </c>
       <c r="I22" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J22" s="14">
         <v>19</v>
       </c>
       <c r="K22" s="15">
-        <v>26.315789473684</v>
+        <v>36.842105263157</v>
       </c>
       <c r="L22" s="15">
-        <v>60</v>
+        <v>73.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>20</v>
+        <v>23.809523809523</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
+        <v>150</v>
+      </c>
+      <c r="I23" s="14">
+        <v>20</v>
+      </c>
+      <c r="J23" s="14">
+        <v>9</v>
+      </c>
+      <c r="K23" s="15">
+        <v>122.222222222222</v>
+      </c>
+      <c r="L23" s="15">
+        <v>25</v>
+      </c>
+      <c r="M23" s="15">
         <v>300</v>
-      </c>
-      <c r="I23" s="14">
-        <v>18</v>
-      </c>
-      <c r="J23" s="14">
-        <v>8</v>
-      </c>
-      <c r="K23" s="15">
-        <v>125</v>
-      </c>
-      <c r="L23" s="15">
-        <v>20</v>
-      </c>
-      <c r="M23" s="15">
-        <v>350</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>8.108108108108</v>
+        <v>-16</v>
       </c>
       <c r="F24" s="14">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="G24" s="14">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.692307692307</v>
+        <v>-3.787878787878</v>
       </c>
       <c r="I24" s="14">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="J24" s="14">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.336302895322</v>
+        <v>-2.320675105485</v>
       </c>
       <c r="L24" s="15">
-        <v>-25.795644891122</v>
+        <v>-28.105590062111</v>
       </c>
       <c r="M24" s="15">
-        <v>19.407008086253</v>
+        <v>16.919191919191</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>13.636363636363</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="G25" s="14">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="H25" s="15">
-        <v>-3.703703703703</v>
+        <v>7.058823529411</v>
       </c>
       <c r="I25" s="14">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="J25" s="14">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="K25" s="15">
-        <v>2.469135802469</v>
+        <v>2.359882005899</v>
       </c>
       <c r="L25" s="15">
-        <v>-38.970588235294</v>
+        <v>-40.683760683760</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>11</v>
+      </c>
+      <c r="D26" s="14">
         <v>6</v>
       </c>
-      <c r="D26" s="14">
-        <v>7</v>
-      </c>
       <c r="E26" s="15">
-        <v>-14.285714285714</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>-34.146341463414</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I26" s="14">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K26" s="15">
-        <v>-15.702479338843</v>
+        <v>-11.023622047244</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.685039370078</v>
+        <v>-19.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>-8.928571428571</v>
+        <v>-2.586206896551</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F28" s="14">
-        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-80</v>
+        <v>-90</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1496,8 +1496,8 @@
       <c r="L29" s="15">
         <v>0</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="15">
+        <v>0</v>
       </c>
       <c r="N29" s="15">
         <v>-91.666666666666</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1537,8 +1537,8 @@
       <c r="L30" s="15">
         <v>0</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="15">
+        <v>0</v>
       </c>
       <c r="N30" s="15">
         <v>-90.909090909090</v>
@@ -1557,14 +1557,14 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>6</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-35.714285714285</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I16" s="14">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J16" s="14">
         <v>49</v>
       </c>
       <c r="K16" s="15">
-        <v>20.408163265306</v>
+        <v>32.653061224489</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.376623376623</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-9.230769230769</v>
+        <v>-4.411764705882</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.997118155619</v>
+        <v>-82.240437158469</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>20</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="I17" s="14">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J17" s="14">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.259259259259</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>2.083333333333</v>
+        <v>0.990099009900</v>
       </c>
       <c r="M17" s="15">
-        <v>172.222222222222</v>
+        <v>155</v>
       </c>
       <c r="N17" s="15">
-        <v>-14.782608695652</v>
+        <v>-18.4</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-88.888888888888</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
         <v>19</v>
       </c>
       <c r="H18" s="15">
-        <v>-52.631578947368</v>
+        <v>-63.157894736842</v>
       </c>
       <c r="I18" s="14">
         <v>52</v>
       </c>
       <c r="J18" s="14">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K18" s="15">
-        <v>-24.637681159420</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.454545454545</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M18" s="15">
-        <v>100</v>
+        <v>79.310344827586</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.785714285714</v>
+        <v>-78.688524590163</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" s="15">
-        <v>14.285714285714</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
         <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>6.122448979591</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="J19" s="14">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.386138613861</v>
+        <v>-10.697674418604</v>
       </c>
       <c r="L19" s="15">
-        <v>-12.682926829268</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M19" s="15">
-        <v>42.063492063492</v>
+        <v>39.130434782608</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.322033898305</v>
+        <v>-39.240506329113</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
-      </c>
-      <c r="D20" s="14">
-        <v>5</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-40</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-58.333333333333</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="14">
         <v>25</v>
       </c>
       <c r="K20" s="15">
-        <v>-52</v>
+        <v>-48</v>
       </c>
       <c r="L20" s="15">
-        <v>-29.411764705882</v>
+        <v>-35</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-18.75</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.258373205741</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-24.324324324324</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="F21" s="17">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G21" s="17">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.4</v>
+        <v>-11.016949152542</v>
       </c>
       <c r="I21" s="17">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="J21" s="17">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.869565217391</v>
+        <v>-11.247443762781</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.090909090909</v>
+        <v>-8.245243128964</v>
       </c>
       <c r="M21" s="18">
-        <v>51.851851851851</v>
+        <v>48.630136986301</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.747702589807</v>
+        <v>-66.067240031274</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>9</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="I22" s="14">
         <v>26</v>
       </c>
       <c r="J22" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K22" s="15">
-        <v>36.842105263157</v>
+        <v>30</v>
       </c>
       <c r="L22" s="15">
-        <v>73.333333333333</v>
+        <v>62.5</v>
       </c>
       <c r="M22" s="15">
-        <v>23.809523809523</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,28 +1230,28 @@
         <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>122.222222222222</v>
+        <v>120</v>
       </c>
       <c r="L23" s="15">
-        <v>25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M23" s="15">
-        <v>300</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="E24" s="15">
-        <v>-16</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="F24" s="14">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="G24" s="14">
         <v>132</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.787878787878</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="J24" s="14">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.320675105485</v>
+        <v>-3.515625</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.105590062111</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M24" s="15">
-        <v>16.919191919191</v>
+        <v>17.339667458432</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.666666666666</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="G25" s="14">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H25" s="15">
-        <v>7.058823529411</v>
+        <v>-3.409090909090</v>
       </c>
       <c r="I25" s="14">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="J25" s="14">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="K25" s="15">
-        <v>2.359882005899</v>
+        <v>1.634877384196</v>
       </c>
       <c r="L25" s="15">
-        <v>-40.683760683760</v>
+        <v>-39.741518578352</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>83.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.090909090909</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I26" s="14">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J26" s="14">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.023622047244</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L26" s="15">
-        <v>-19.285714285714</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="M26" s="15">
-        <v>-2.586206896551</v>
+        <v>2.564102564102</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>2</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>0</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
-        <v>-90</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>-60</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="L28" s="15">
-        <v>-28.571428571428</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>6</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>18.181818181818</v>
+        <v>30</v>
       </c>
       <c r="I16" s="14">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J16" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="K16" s="15">
-        <v>32.653061224489</v>
+        <v>23.636363636363</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.072289156626</v>
       </c>
       <c r="M16" s="15">
-        <v>-4.411764705882</v>
+        <v>-6.849315068493</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.240437158469</v>
+        <v>-82.697201017811</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-63.636363636363</v>
+        <v>350</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.518518518518</v>
+        <v>-12.5</v>
       </c>
       <c r="I17" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J17" s="14">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.285714285714</v>
+        <v>-8.264462809917</v>
       </c>
       <c r="L17" s="15">
-        <v>0.990099009900</v>
+        <v>3.738317757009</v>
       </c>
       <c r="M17" s="15">
-        <v>155</v>
+        <v>141.304347826087</v>
       </c>
       <c r="N17" s="15">
-        <v>-18.4</v>
+        <v>-13.953488372093</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
         <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H18" s="15">
-        <v>-63.157894736842</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J18" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="K18" s="15">
-        <v>-29.729729729729</v>
+        <v>-30.379746835443</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.771929824561</v>
+        <v>-3.508771929824</v>
       </c>
       <c r="M18" s="15">
-        <v>79.310344827586</v>
+        <v>83.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.688524590163</v>
+        <v>-78.346456692913</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>30</v>
       </c>
       <c r="F19" s="14">
         <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H19" s="15">
-        <v>14.285714285714</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I19" s="14">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="J19" s="14">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.697674418604</v>
+        <v>-8.444444444444</v>
       </c>
       <c r="L19" s="15">
-        <v>-11.111111111111</v>
+        <v>-10.434782608695</v>
       </c>
       <c r="M19" s="15">
-        <v>39.130434782608</v>
+        <v>44.055944055944</v>
       </c>
       <c r="N19" s="15">
-        <v>-39.240506329113</v>
+        <v>-37.764350453172</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-54.545454545454</v>
+        <v>-37.5</v>
       </c>
       <c r="I20" s="14">
         <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K20" s="15">
-        <v>-48</v>
+        <v>-50</v>
       </c>
       <c r="L20" s="15">
-        <v>-35</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.117647058823</v>
+        <v>-94.347826086956</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.689655172413</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G21" s="17">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.016949152542</v>
+        <v>-1.834862385321</v>
       </c>
       <c r="I21" s="17">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="J21" s="17">
-        <v>489</v>
+        <v>513</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.247443762781</v>
+        <v>-9.746588693957</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.245243128964</v>
+        <v>-7.4</v>
       </c>
       <c r="M21" s="18">
-        <v>48.630136986301</v>
+        <v>49.354838709677</v>
       </c>
       <c r="N21" s="18">
-        <v>-66.067240031274</v>
+        <v>-65.550595238095</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="I22" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J22" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K22" s="15">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="L22" s="15">
-        <v>62.5</v>
+        <v>64.705882352941</v>
       </c>
       <c r="M22" s="15">
-        <v>18.181818181818</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>120</v>
+        <v>91.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>29.411764705882</v>
+        <v>35.294117647058</v>
       </c>
       <c r="M23" s="15">
-        <v>266.666666666667</v>
+        <v>283.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E24" s="15">
-        <v>-18.421052631578</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G24" s="14">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.333333333333</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I24" s="14">
-        <v>494</v>
+        <v>524</v>
       </c>
       <c r="J24" s="14">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.515625</v>
+        <v>-4.379562043795</v>
       </c>
       <c r="L24" s="15">
-        <v>-27.777777777777</v>
+        <v>-28.219178082191</v>
       </c>
       <c r="M24" s="15">
-        <v>17.339667458432</v>
+        <v>18.018018018018</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D25" s="14">
         <v>28</v>
       </c>
       <c r="E25" s="15">
-        <v>-10.714285714285</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G25" s="14">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H25" s="15">
-        <v>-3.409090909090</v>
+        <v>-1.075268817204</v>
       </c>
       <c r="I25" s="14">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="J25" s="14">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="K25" s="15">
-        <v>1.634877384196</v>
+        <v>1.012658227848</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.741518578352</v>
+        <v>-39.176829268292</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-22.222222222222</v>
+        <v>54.545454545454</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.529411764705</v>
+        <v>27.272727272727</v>
       </c>
       <c r="I26" s="14">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="J26" s="14">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.764705882352</v>
+        <v>-6.122448979591</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.808219178082</v>
+        <v>-10.967741935483</v>
       </c>
       <c r="M26" s="15">
-        <v>2.564102564102</v>
+        <v>4.545454545454</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1447,13 +1447,13 @@
         <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K28" s="15">
-        <v>-53.571428571428</v>
+        <v>-59.375</v>
       </c>
       <c r="L28" s="15">
-        <v>-13.333333333333</v>
+        <v>-18.75</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,10 +1570,10 @@
         <v>5</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="L31" s="15">
         <v>25</v>

--- a/data/source/weekly/cs-en-us-084pct.xlsx
+++ b/data/source/weekly/cs-en-us-084pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>66.666666666666</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H16" s="15">
-        <v>30</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J16" s="14">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K16" s="15">
-        <v>23.636363636363</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-18.072289156626</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="15">
-        <v>-6.849315068493</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.697201017811</v>
+        <v>-82.481751824817</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>-12.5</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I17" s="14">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="J17" s="14">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.264462809917</v>
+        <v>-5.6</v>
       </c>
       <c r="L17" s="15">
-        <v>3.738317757009</v>
+        <v>3.508771929824</v>
       </c>
       <c r="M17" s="15">
-        <v>141.304347826087</v>
+        <v>151.063829787234</v>
       </c>
       <c r="N17" s="15">
-        <v>-13.953488372093</v>
+        <v>-16.312056737588</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
         <v>5</v>
       </c>
-      <c r="E18" s="15">
-        <v>-60</v>
-      </c>
-      <c r="F18" s="14">
-        <v>10</v>
-      </c>
       <c r="G18" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-54.545454545454</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J18" s="14">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.379746835443</v>
+        <v>-30</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.508771929824</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="M18" s="15">
-        <v>83.333333333333</v>
+        <v>75</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.346456692913</v>
+        <v>-78.787878787878</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>30</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G19" s="14">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="H19" s="15">
-        <v>27.272727272727</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I19" s="14">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="J19" s="14">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.444444444444</v>
+        <v>-8.786610878661</v>
       </c>
       <c r="L19" s="15">
-        <v>-10.434782608695</v>
+        <v>-11.740890688259</v>
       </c>
       <c r="M19" s="15">
-        <v>44.055944055944</v>
+        <v>47.297297297297</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.764350453172</v>
+        <v>-36.070381231671</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-37.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J20" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.909090909090</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.529411764705</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.347826086956</v>
+        <v>-93.775933609958</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E21" s="18">
-        <v>16.666666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.834862385321</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="I21" s="17">
-        <v>463</v>
+        <v>489</v>
       </c>
       <c r="J21" s="17">
-        <v>513</v>
+        <v>545</v>
       </c>
       <c r="K21" s="18">
-        <v>-9.746588693957</v>
+        <v>-10.275229357798</v>
       </c>
       <c r="L21" s="18">
-        <v>-7.4</v>
+        <v>-9.444444444444</v>
       </c>
       <c r="M21" s="18">
-        <v>49.354838709677</v>
+        <v>51.863354037267</v>
       </c>
       <c r="N21" s="18">
-        <v>-65.550595238095</v>
+        <v>-65.195729537366</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>75</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I22" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J22" s="14">
         <v>22</v>
       </c>
       <c r="K22" s="15">
-        <v>27.272727272727</v>
+        <v>45.454545454545</v>
       </c>
       <c r="L22" s="15">
-        <v>64.705882352941</v>
+        <v>88.235294117647</v>
       </c>
       <c r="M22" s="15">
-        <v>16.666666666666</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,14 +1220,14 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>2</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-50</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>5</v>
@@ -1248,7 +1248,7 @@
         <v>91.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>35.294117647058</v>
+        <v>21.052631578947</v>
       </c>
       <c r="M23" s="15">
         <v>283.333333333333</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>6.060606060606</v>
       </c>
       <c r="F24" s="14">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G24" s="14">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.764705882352</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="I24" s="14">
-        <v>524</v>
+        <v>558</v>
       </c>
       <c r="J24" s="14">
-        <v>548</v>
+        <v>581</v>
       </c>
       <c r="K24" s="15">
-        <v>-4.379562043795</v>
+        <v>-3.958691910499</v>
       </c>
       <c r="L24" s="15">
-        <v>-28.219178082191</v>
+        <v>-27.154046997389</v>
       </c>
       <c r="M24" s="15">
-        <v>18.018018018018</v>
+        <v>17.721518987341</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D25" s="14">
         <v>28</v>
       </c>
       <c r="E25" s="15">
-        <v>-3.571428571428</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G25" s="14">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H25" s="15">
-        <v>-1.075268817204</v>
+        <v>-8.080808080808</v>
       </c>
       <c r="I25" s="14">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="J25" s="14">
-        <v>395</v>
+        <v>423</v>
       </c>
       <c r="K25" s="15">
-        <v>1.012658227848</v>
+        <v>0.236406619385</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.176829268292</v>
+        <v>-38.992805755395</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>54.545454545454</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
         <v>42</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>27.272727272727</v>
+        <v>20</v>
       </c>
       <c r="I26" s="14">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="J26" s="14">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.122448979591</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.967741935483</v>
+        <v>-13.253012048192</v>
       </c>
       <c r="M26" s="15">
-        <v>4.545454545454</v>
+        <v>-0.689655172413</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>10</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L27" s="15">
         <v>233.333333333333</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>4</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>3</v>
-      </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="14">
         <v>32</v>
       </c>
       <c r="K28" s="15">
-        <v>-59.375</v>
+        <v>-56.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-18.75</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>25</v>
       </c>
       <c r="L31" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
